--- a/codigos_unicos.xlsx
+++ b/codigos_unicos.xlsx
@@ -43,10 +43,10 @@
     <t xml:space="preserve">SERVICIO DE EMPASTES Y ENCUADERNACION</t>
   </si>
   <si>
-    <t xml:space="preserve">Servicio del limpieza interna y externa y externa de vidrios</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Arriendo de impresoras multifuncionales- Sección Control Bienes</t>
+    <t xml:space="preserve">Servicio del limpieza interna y externa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arriendo de impresoras multifuncionales</t>
   </si>
   <si>
     <t xml:space="preserve">Mantencion Control de Acceso MINVU (36 meses)</t>
@@ -136,10 +136,10 @@
     <t xml:space="preserve">Licitación Pública para la Contratación de los Servicios de Jardineria</t>
   </si>
   <si>
-    <t xml:space="preserve">SERVICIO DE MUDANZA - SECCION CONTROL BIENES</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RECARGA DE GAS LICUADO - JARDIN INFANTIL</t>
+    <t xml:space="preserve">SERVICIO DE MUDANZA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RECARGA DE GAS LICUADO</t>
   </si>
   <si>
     <t xml:space="preserve">SUSCRIPCION APLICACIONES DE EDICION Y TRANSCRIPCION AUDIOVIDEO</t>
@@ -224,7 +224,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -246,6 +246,14 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <u val="single"/>
@@ -298,7 +306,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -312,6 +320,14 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -515,10 +531,10 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
     </row>
@@ -590,7 +606,7 @@
       <c r="A10" s="1" t="n">
         <v>2903</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="5" t="s">
         <v>10</v>
       </c>
     </row>
